--- a/data/trans_dic/IP12B$alergia-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,16</t>
+          <t>0,0; 24,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,5</t>
+          <t>0,0; 38,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,13</t>
+          <t>0,0; 50,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,51</t>
+          <t>0,0; 19,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 26,72</t>
+          <t>2,89; 23,16</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,64</t>
+          <t>0,0; 22,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,65</t>
+          <t>0,0; 21,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 9,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,71</t>
+          <t>0,0; 16,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,66</t>
+          <t>0,0; 18,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,86</t>
+          <t>0,0; 13,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,04</t>
+          <t>0,0; 12,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,95</t>
+          <t>0,0; 36,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,39</t>
+          <t>0,0; 20,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,74</t>
+          <t>0,0; 40,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,66</t>
+          <t>0,0; 27,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,27</t>
+          <t>0,0; 28,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,28</t>
+          <t>0,0; 28,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,36</t>
+          <t>0,0; 23,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,89</t>
+          <t>0,0; 17,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 27,26</t>
+          <t>3,07; 27,46</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,0</t>
+          <t>0,0; 38,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,79</t>
+          <t>0,0; 45,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,79</t>
+          <t>0,0; 41,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,33</t>
+          <t>0,0; 33,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,73</t>
+          <t>0,0; 28,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,17</t>
+          <t>0,0; 17,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,54</t>
+          <t>0,0; 19,41</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,21</t>
+          <t>1,45; 12,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 15,18</t>
+          <t>2,37; 14,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,06</t>
+          <t>1,27; 10,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,95</t>
+          <t>2,35; 14,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,14</t>
+          <t>1,4; 12,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,9</t>
+          <t>1,59; 8,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,4</t>
+          <t>2,03; 9,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 11,19</t>
+          <t>2,82; 11,34</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2916</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5100</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3713</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6026</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>556; 4461</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1775</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3551</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4358</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3287</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4551</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4706</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5704</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2570</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3087</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3886</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2876</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4867</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2733</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2872</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4014</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4876</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4182</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>800; 7160</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3068</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3860</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3204</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5040</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4484</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4294</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3238</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6230</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>637; 5594</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5009</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7851</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>592; 5107</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1492; 9129</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>669; 6180</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1438; 8142</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2532; 11980</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2904; 11675</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$alergia-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,58</t>
+          <t>0,0; 24,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,54</t>
+          <t>0,0; 39,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,21</t>
+          <t>0,0; 44,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,31</t>
+          <t>0,0; 17,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 23,16</t>
+          <t>2,93; 26,38</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,11</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,53</t>
+          <t>0,0; 23,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 11,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,75</t>
+          <t>0,0; 13,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,12</t>
+          <t>0,0; 17,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,19</t>
+          <t>0,0; 13,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,58</t>
+          <t>0,0; 11,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,17</t>
+          <t>0,0; 34,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,53</t>
+          <t>0,0; 24,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,46</t>
+          <t>0,0; 42,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,42</t>
+          <t>0,0; 25,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,09</t>
+          <t>0,0; 26,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,58</t>
+          <t>0,0; 29,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,54</t>
+          <t>0,0; 21,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,26</t>
+          <t>0,0; 17,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 27,46</t>
+          <t>3,17; 24,76</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,61</t>
+          <t>0,0; 36,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,36</t>
+          <t>0,0; 43,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,12</t>
+          <t>0,0; 41,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,63</t>
+          <t>0,0; 29,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,49</t>
+          <t>0,0; 28,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,85</t>
+          <t>0,0; 23,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,41</t>
+          <t>0,0; 24,19</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,75</t>
+          <t>1,45; 13,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 14,24</t>
+          <t>1,82; 13,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,93</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,36</t>
+          <t>2,46; 15,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,91</t>
+          <t>1,37; 13,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,99</t>
+          <t>1,99; 9,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,59</t>
+          <t>1,84; 9,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,34</t>
+          <t>2,9; 11,42</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2916</t>
+          <t>0; 2936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5100</t>
+          <t>0; 5191</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3713</t>
+          <t>0; 3327</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6026</t>
+          <t>0; 5386</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>556; 4461</t>
+          <t>565; 5081</t>
         </is>
       </c>
     </row>
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3551</t>
+          <t>0; 3354</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4358</t>
+          <t>0; 4668</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2111</t>
+          <t>0; 2534</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3287</t>
+          <t>0; 2638</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4551</t>
+          <t>0; 4456</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4706</t>
+          <t>0; 4641</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5704</t>
+          <t>0; 5203</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2570</t>
+          <t>0; 2090</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3886</t>
+          <t>0; 3758</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2876</t>
+          <t>0; 3494</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4867</t>
+          <t>0; 5120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2733</t>
+          <t>0; 2531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2872</t>
+          <t>0; 2752</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4014</t>
+          <t>0; 4144</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4876</t>
+          <t>0; 4424</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4182</t>
+          <t>0; 4214</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>800; 7160</t>
+          <t>828; 6455</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3068</t>
+          <t>0; 2897</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3860</t>
+          <t>0; 3729</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3204</t>
+          <t>0; 3208</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5040</t>
+          <t>0; 4472</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4484</t>
+          <t>0; 4478</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>0; 5558</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3238</t>
+          <t>0; 4034</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>637; 5594</t>
+          <t>635; 5891</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5009</t>
+          <t>0; 5198</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1306; 7851</t>
+          <t>1004; 7595</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>592; 5107</t>
+          <t>0; 4541</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1492; 9129</t>
+          <t>1560; 9698</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>669; 6180</t>
+          <t>657; 6443</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1438; 8142</t>
+          <t>1798; 8169</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2532; 11980</t>
+          <t>2299; 11711</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2904; 11675</t>
+          <t>2982; 11763</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$alergia-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 40,5</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 45,13</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 24,74</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 39,23</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,99</t>
+          <t>0,0; 26,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,26</t>
+          <t>0,0; 18,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,93; 26,38</t>
+          <t>2,95; 26,72</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 16,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,06</t>
+          <t>0,0; 18,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,44</t>
+          <t>0,0; 18,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,74</t>
+          <t>0,0; 18,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,01</t>
+          <t>0,0; 11,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,47</t>
+          <t>0,0; 12,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,36%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14,84%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,98</t>
+          <t>0,0; 30,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,93</t>
+          <t>0,0; 27,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,57</t>
+          <t>0,0; 29,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,39</t>
+          <t>0,0; 40,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,92</t>
+          <t>0,0; 20,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,51</t>
+          <t>0,0; 42,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,36</t>
+          <t>0,0; 22,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,39</t>
+          <t>0,0; 16,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 24,76</t>
+          <t>3,39; 27,26</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,96%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,07%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,46</t>
+          <t>0,0; 41,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 30,33</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 43,83</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,16</t>
+          <t>0,0; 33,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,46</t>
+          <t>0,0; 24,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,1</t>
+          <t>0,0; 16,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,19</t>
+          <t>0,0; 22,54</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,83%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,56%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,43</t>
+          <t>1,25; 12,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,48</t>
+          <t>2,62; 14,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 13,78</t>
+          <t>1,38; 13,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>1,45; 13,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,26</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 13,46</t>
+          <t>2,37; 15,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,02</t>
+          <t>1,57; 8,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,38</t>
+          <t>2,06; 9,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,42</t>
+          <t>2,88; 11,19</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,27 +1316,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>560</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1422,27 +1422,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 5360</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3337</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2936</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5191</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3327</t>
+          <t>0; 3105</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5386</t>
+          <t>0; 5776</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>565; 5081</t>
+          <t>568; 5147</t>
         </is>
       </c>
     </row>
@@ -1484,22 +1484,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>696</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>875</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>502</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3354</t>
+          <t>0; 3279</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4668</t>
+          <t>0; 4687</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2534</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2638</t>
+          <t>0; 2993</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4456</t>
+          <t>0; 3776</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2641</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>0; 4230</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5203</t>
+          <t>0; 5461</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2090</t>
+          <t>0; 2598</t>
         </is>
       </c>
     </row>
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1785</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3758</t>
+          <t>0; 3056</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3494</t>
+          <t>0; 2787</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5120</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2531</t>
+          <t>0; 4399</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2752</t>
+          <t>0; 2856</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4144</t>
+          <t>0; 5141</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4424</t>
+          <t>0; 4631</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4214</t>
+          <t>0; 4092</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>828; 6455</t>
+          <t>883; 7108</t>
         </is>
       </c>
     </row>
@@ -1805,27 +1805,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>984</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2897</t>
+          <t>0; 3257</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0; 4545</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3729</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3208</t>
+          <t>0; 2622</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4472</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3216</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4478</t>
+          <t>0; 3892</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5558</t>
+          <t>0; 3890</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4034</t>
+          <t>0; 3760</t>
         </is>
       </c>
     </row>
@@ -1968,27 +1968,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>2120</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1570</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3618</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4187</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>635; 5891</t>
+          <t>586; 5633</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5198</t>
+          <t>1668; 9499</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1004; 7595</t>
+          <t>659; 6287</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4541</t>
+          <t>634; 5796</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1560; 9698</t>
+          <t>0; 4880</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>657; 6443</t>
+          <t>1305; 8368</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1798; 8169</t>
+          <t>1425; 8063</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2299; 11711</t>
+          <t>2571; 11735</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2982; 11763</t>
+          <t>2964; 11520</t>
         </is>
       </c>
     </row>
